--- a/data/archive/2026-10-05.xlsx
+++ b/data/archive/2026-10-05.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Jobs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -645,7 +645,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05 19:10 UTC</t>
+          <t>2026-10-05 20:05 UTC</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05 19:10 UTC</t>
+          <t>2026-10-05 20:05 UTC</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
@@ -754,12 +754,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Chime</t>
+          <t>Nuro</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer, Infrastructure Platform</t>
+          <t>New Grad Software Engineer, Routing</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -769,12 +769,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA; New York, NY, USA; San Francisco, CA, USA</t>
+          <t>Mountain View, California (HQ)</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -784,17 +784,17 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8859182002</t>
+          <t>8248317</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/chime/jobs/8859182002?gh_jid=8859182002</t>
+          <t>https://nuro.ai/careersitem?gh_jid=8248317</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05 19:10 UTC</t>
+          <t>2026-10-05 20:05 UTC</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -841,12 +841,12 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Notion</t>
+          <t>Chime</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer Intern, Mobile (Winter 2027)</t>
+          <t>Software Engineer, Infrastructure Platform</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -856,38 +856,42 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, California; New York, New York; New York, New York, United States; San Francisco, California, United States</t>
+          <t>Chicago, IL, USA; New York, NY, USA; San Francisco, CA, USA</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr"/>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>2b587e66-deac-421a-a824-9415ba78b5a7</t>
+          <t>8859182002</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>ashby</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/notion/2b587e66-deac-421a-a824-9415ba78b5a7</t>
+          <t>https://boards.greenhouse.io/chime/jobs/8859182002?gh_jid=8859182002</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -902,7 +906,7 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05 19:10 UTC</t>
+          <t>2026-10-05 20:05 UTC</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
@@ -924,12 +928,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Scale AI</t>
+          <t>Notion</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer, Public Sector - New Grad</t>
+          <t>Software Engineer Intern, Mobile (Winter 2027)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -939,42 +943,38 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>San Francisco, California; New York, New York; New York, New York, United States; San Francisco, California, United States</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4736426005</t>
+          <t>2b587e66-deac-421a-a824-9415ba78b5a7</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>ashby</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/scaleai/jobs/4736426005</t>
+          <t>https://jobs.ashbyhq.com/notion/2b587e66-deac-421a-a824-9415ba78b5a7</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05 19:10 UTC</t>
+          <t>2026-10-05 20:05 UTC</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1011,12 +1011,12 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Affirm</t>
+          <t>Scale AI</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer Intern (Summer 2027)</t>
+          <t>Software Engineer, Public Sector - New Grad</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -1026,32 +1026,32 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, California, United States</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>8011590003</t>
+          <t>4736426005</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/8011590003</t>
+          <t>https://job-boards.greenhouse.io/scaleai/jobs/4736426005</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05 19:10 UTC</t>
+          <t>2026-10-05 20:05 UTC</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer (Machine Learning) Intern (Summer 2027)</t>
+          <t>Software Engineer Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8008645003</t>
+          <t>8011590003</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/8008645003</t>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/8011590003</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05 19:10 UTC</t>
+          <t>2026-10-05 20:05 UTC</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Staff Software Engineer, Backend (Search)</t>
+          <t>Software Engineer (Machine Learning) Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Remote US</t>
+          <t>San Francisco, California, United States</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -1210,22 +1210,22 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>8005406003</t>
+          <t>8008645003</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/8005406003</t>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/8008645003</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05 19:10 UTC</t>
+          <t>2026-10-05 20:05 UTC</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
@@ -1272,12 +1272,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Affirm</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Systems Software Engineer - New College Grad 2026</t>
+          <t>Staff Software Engineer, Backend (Search)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1287,12 +1287,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>US, OR, Hillsboro</t>
+          <t>Remote US</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1305,20 +1305,24 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>JR2017083</t>
+          <t>8005406003</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-OR-Hillsboro/Systems-Software-Engineer---New-College-Grad-2026_JR2017083</t>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/8005406003</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1333,7 +1337,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05 19:12 UTC</t>
+          <t>2026-10-05 20:05 UTC</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1355,22 +1359,22 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Product Engineering Intern</t>
+          <t>Systems Software Engineer - New College Grad 2026</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Product Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>McLean, VA</t>
+          <t>US, OR, Hillsboro</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -1380,18 +1384,18 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr"/>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>R0250655</t>
+          <t>JR2017083</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1401,7 +1405,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/McLean-VA/Product-Engineering-Intern_R0250655</t>
+          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-OR-Hillsboro/Systems-Software-Engineer---New-College-Grad-2026_JR2017083</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -1416,7 +1420,7 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05 19:14 UTC</t>
+          <t>2026-10-05 20:08 UTC</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
@@ -1443,17 +1447,17 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Cybersecurity Engineer, Junior</t>
+          <t>Product Engineering Intern</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Security Engineer</t>
+          <t>Product Engineer</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>El Segundo, CA</t>
+          <t>McLean, VA</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1463,63 +1467,146 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr">
         <is>
+          <t>R0250655</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/McLean-VA/Product-Engineering-Intern_R0250655</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05 20:10 UTC</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Cybersecurity Engineer, Junior</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Security Engineer</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>El Segundo, CA</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr"/>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
           <t>R0250290</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J13" s="4" t="inlineStr">
         <is>
           <t>workday</t>
         </is>
       </c>
-      <c r="K12" s="3" t="inlineStr">
+      <c r="K13" s="3" t="inlineStr">
         <is>
           <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/El-Segundo-CA/Cybersecurity-Engineer--Junior_R0250290</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="L13" s="4" t="inlineStr">
         <is>
           <t>☐ Not Applied</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="M13" s="4" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-05 19:14 UTC</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 20:10 UTC</t>
+        </is>
+      </c>
+      <c r="O13" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P13" s="4" t="inlineStr">
         <is>
           <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
         </is>
       </c>
-      <c r="Q12" s="2" t="inlineStr">
+      <c r="Q13" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q12"/>
+  <autoFilter ref="A1:Q13"/>
   <dataValidations count="2">
     <dataValidation sqref="L2:L500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Applied" error="Select a value from the list" type="list">
       <formula1>"☐ Not Applied,☑ Applied"</formula1>
@@ -1540,6 +1627,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
